--- a/Dependencies/Takasugi_2024/percent_validated_genomehomol_SAAP.xlsx
+++ b/Dependencies/Takasugi_2024/percent_validated_genomehomol_SAAP.xlsx
@@ -465,7 +465,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>32.13610586011342</v>
+        <v>42.15500945179584</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -488,7 +488,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>22.52252252252252</v>
+        <v>41.74174174174174</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>50.54744525547446</v>
+        <v>60.4014598540146</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -534,7 +534,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>40.28776978417266</v>
+        <v>44.60431654676259</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.70967741935484</v>
+        <v>34.83870967741935</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -580,7 +580,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>45.20884520884521</v>
+        <v>50.85995085995086</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>39.4273127753304</v>
+        <v>56.6079295154185</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>36.12040133779264</v>
+        <v>45.81939799331104</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
